--- a/backend/data/financials_by_company/04T.F.xlsx
+++ b/backend/data/financials_by_company/04T.F.xlsx
@@ -4391,10 +4391,8 @@
           <t>Hangzhou</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>310011</t>
-        </is>
+      <c r="D2" t="n">
+        <v>310011</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4610,7 +4608,7 @@
         <v>-9306000</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
         <v>-19.523</v>
@@ -4836,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA2" t="n">
         <v>-0.0047999993</v>
